--- a/lang/nl/headTags.xlsx
+++ b/lang/nl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1209</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1966">
   <si>
     <t>en</t>
   </si>
@@ -4666,6 +4666,18 @@
     <t>Shulker</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (Geïnspireerd)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Zeef (Vanille)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -5452,6 +5464,9 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -5714,6 +5729,12 @@
   </si>
   <si>
     <t>Winter</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>Wintercollectie</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -6240,7 +6261,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1205"/>
+  <dimension ref="A1:B1209"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13956,28 +13977,28 @@
         <v>1551</v>
       </c>
       <c r="B964" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B965" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="B966" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B967" t="s">
         <v>1556</v>
@@ -14004,28 +14025,28 @@
         <v>1561</v>
       </c>
       <c r="B970" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B971" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B972" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B973" t="s">
         <v>1566</v>
@@ -14076,20 +14097,20 @@
         <v>1577</v>
       </c>
       <c r="B979" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B980" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B981" t="s">
         <v>1581</v>
@@ -14188,28 +14209,28 @@
         <v>1604</v>
       </c>
       <c r="B993" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B994" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="B995" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B996" t="s">
         <v>1609</v>
@@ -14220,68 +14241,68 @@
         <v>1610</v>
       </c>
       <c r="B997" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B998" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B999" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="B1000" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="B1001" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="B1002" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="B1003" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="B1004" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B1005" t="s">
         <v>1620</v>
@@ -14300,20 +14321,20 @@
         <v>1623</v>
       </c>
       <c r="B1007" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B1008" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B1009" t="s">
         <v>1627</v>
@@ -14324,28 +14345,28 @@
         <v>1628</v>
       </c>
       <c r="B1010" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B1011" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B1012" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B1013" t="s">
         <v>1633</v>
@@ -14356,20 +14377,20 @@
         <v>1634</v>
       </c>
       <c r="B1014" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1015" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1016" t="s">
         <v>1638</v>
@@ -14380,84 +14401,84 @@
         <v>1639</v>
       </c>
       <c r="B1017" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1018" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="B1019" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="B1020" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="B1021" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1022" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B1023" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="B1024" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="B1025" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B1026" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B1027" t="s">
         <v>1652</v>
@@ -14484,28 +14505,28 @@
         <v>1657</v>
       </c>
       <c r="B1030" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B1031" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="B1032" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1033" t="s">
         <v>1662</v>
@@ -14516,20 +14537,20 @@
         <v>1663</v>
       </c>
       <c r="B1034" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B1035" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B1036" t="s">
         <v>1667</v>
@@ -14548,44 +14569,44 @@
         <v>1670</v>
       </c>
       <c r="B1038" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B1039" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1040" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1041" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="B1042" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1043" t="s">
         <v>1678</v>
@@ -14596,76 +14617,76 @@
         <v>1679</v>
       </c>
       <c r="B1044" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1045" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="B1046" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="B1047" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1048" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1049" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B1050" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1051" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1052" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1053" t="s">
         <v>1692</v>
@@ -14740,20 +14761,20 @@
         <v>1709</v>
       </c>
       <c r="B1062" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1063" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1064" t="s">
         <v>1713</v>
@@ -14940,20 +14961,20 @@
         <v>1758</v>
       </c>
       <c r="B1087" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B1088" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B1089" t="s">
         <v>1762</v>
@@ -14972,28 +14993,28 @@
         <v>1765</v>
       </c>
       <c r="B1091" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B1092" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="B1093" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B1094" t="s">
         <v>1770</v>
@@ -15020,36 +15041,36 @@
         <v>1775</v>
       </c>
       <c r="B1097" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B1098" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B1099" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B1100" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B1101" t="s">
         <v>1782</v>
@@ -15092,31 +15113,31 @@
         <v>1791</v>
       </c>
       <c r="B1106" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1107" t="s">
-        <v>1791</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="B1108" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B1109" t="s">
         <v>1795</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>1796</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
@@ -15148,20 +15169,20 @@
         <v>1803</v>
       </c>
       <c r="B1113" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B1114" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B1115" t="s">
         <v>1807</v>
@@ -15180,44 +15201,44 @@
         <v>1810</v>
       </c>
       <c r="B1117" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1118" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B1119" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B1120" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1121" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1122" t="s">
         <v>1818</v>
@@ -15228,196 +15249,196 @@
         <v>1819</v>
       </c>
       <c r="B1123" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1821</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1822</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1823</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1824</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1825</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1827</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1828</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1829</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1830</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1831</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1832</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1833</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1834</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1835</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1836</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1837</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1838</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1839</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1840</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1841</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1843</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1136" t="s">
         <v>1845</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B1137" t="s">
         <v>1847</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1849</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1851</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B1140" t="s">
         <v>1853</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B1141" t="s">
         <v>1855</v>
-      </c>
-      <c r="B1141" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B1142" t="s">
         <v>1857</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>1858</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B1143" t="s">
         <v>1859</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1144" t="s">
         <v>1861</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1145" t="s">
         <v>1863</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1146" t="s">
         <v>1865</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>1866</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="B1147" t="s">
         <v>1867</v>
@@ -15428,44 +15449,44 @@
         <v>1868</v>
       </c>
       <c r="B1148" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B1149" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="B1150" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B1151" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="B1152" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B1153" t="s">
         <v>1875</v>
@@ -15484,28 +15505,28 @@
         <v>1877</v>
       </c>
       <c r="B1155" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B1156" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="B1157" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1158" t="s">
         <v>1882</v>
@@ -15540,44 +15561,44 @@
         <v>1888</v>
       </c>
       <c r="B1162" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B1163" t="s">
         <v>1890</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>1891</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B1164" t="s">
         <v>1892</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>1893</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B1165" t="s">
         <v>1894</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>1895</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1166" t="s">
         <v>1896</v>
-      </c>
-      <c r="B1166" t="s">
-        <v>1897</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B1167" t="s">
         <v>1898</v>
@@ -15604,36 +15625,36 @@
         <v>1903</v>
       </c>
       <c r="B1170" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B1171" t="s">
         <v>1905</v>
-      </c>
-      <c r="B1171" t="s">
-        <v>1906</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B1172" t="s">
         <v>1907</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>1908</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1173" t="s">
         <v>1909</v>
-      </c>
-      <c r="B1173" t="s">
-        <v>1910</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B1174" t="s">
         <v>1911</v>
@@ -15644,124 +15665,124 @@
         <v>1912</v>
       </c>
       <c r="B1175" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1176" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="B1177" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="B1178" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="B1179" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="B1180" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B1181" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="B1182" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1183" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="B1184" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="B1185" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="B1186" t="s">
-        <v>1926</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B1187" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="B1188" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1189" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1190" t="s">
         <v>1933</v>
@@ -15772,36 +15793,36 @@
         <v>1934</v>
       </c>
       <c r="B1191" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1192" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B1193" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B1194" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B1195" t="s">
         <v>1941</v>
@@ -15820,12 +15841,12 @@
         <v>1944</v>
       </c>
       <c r="B1197" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B1198" t="s">
         <v>1946</v>
@@ -15852,43 +15873,75 @@
         <v>1951</v>
       </c>
       <c r="B1201" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="B1202" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="B1203" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="B1204" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B1205" t="s">
         <v>1958</v>
       </c>
     </row>
+    <row r="1206" spans="1:2">
+      <c r="A1206" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:2">
+      <c r="A1207" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:2">
+      <c r="A1208" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:2">
+      <c r="A1209" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>1965</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1205"/>
+  <autoFilter ref="A1:B1209"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
